--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -1024,10 +1024,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121144101</v>
+        <v>121145072</v>
       </c>
       <c r="B5" t="n">
-        <v>79679</v>
+        <v>98071</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,38 +1036,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592498</v>
+        <v>592412</v>
       </c>
       <c r="R5" t="n">
-        <v>7057382</v>
+        <v>7057010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121145072</v>
+        <v>121145444</v>
       </c>
       <c r="B6" t="n">
         <v>98071</v>
@@ -1171,7 +1175,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1180,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592412</v>
+        <v>592480</v>
       </c>
       <c r="R6" t="n">
-        <v>7057010</v>
+        <v>7057011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1225,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121145444</v>
+        <v>121144101</v>
       </c>
       <c r="B7" t="n">
-        <v>98071</v>
+        <v>79679</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1264,42 +1268,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592480</v>
+        <v>592498</v>
       </c>
       <c r="R7" t="n">
-        <v>7057011</v>
+        <v>7057382</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121145668</v>
+        <v>121145281</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,19 +710,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592435</v>
+        <v>592450</v>
       </c>
       <c r="R2" t="n">
-        <v>7057094</v>
+        <v>7056929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121144798</v>
+        <v>121144953</v>
       </c>
       <c r="B3" t="n">
-        <v>78334</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,38 +803,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592367</v>
+        <v>592355</v>
       </c>
       <c r="R3" t="n">
-        <v>7057196</v>
+        <v>7057066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121144873</v>
+        <v>121144798</v>
       </c>
       <c r="B4" t="n">
-        <v>98071</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,47 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592361</v>
+        <v>592367</v>
       </c>
       <c r="R4" t="n">
-        <v>7057138</v>
+        <v>7057196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,22 +1007,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121145072</v>
+        <v>121144897</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,19 +1054,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592412</v>
+        <v>592373</v>
       </c>
       <c r="R5" t="n">
-        <v>7057010</v>
+        <v>7057122</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1113,7 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121145444</v>
+        <v>121145874</v>
       </c>
       <c r="B6" t="n">
-        <v>98071</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,42 +1147,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592480</v>
+        <v>592503</v>
       </c>
       <c r="R6" t="n">
-        <v>7057011</v>
+        <v>7057245</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1229,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,10 +1247,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121144101</v>
+        <v>121145366</v>
       </c>
       <c r="B7" t="n">
-        <v>79679</v>
+        <v>98081</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1268,38 +1259,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592498</v>
+        <v>592468</v>
       </c>
       <c r="R7" t="n">
-        <v>7057382</v>
+        <v>7056982</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,22 +1356,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121145041</v>
+        <v>121145481</v>
       </c>
       <c r="B8" t="n">
-        <v>98071</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,30 +1380,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1412,10 +1417,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592409</v>
+        <v>592501</v>
       </c>
       <c r="R8" t="n">
-        <v>7057036</v>
+        <v>7057009</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1447,7 +1452,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1457,7 +1462,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,10 +1489,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121144921</v>
+        <v>121145312</v>
       </c>
       <c r="B9" t="n">
-        <v>98071</v>
+        <v>78337</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,42 +1501,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592376</v>
+        <v>592474</v>
       </c>
       <c r="R9" t="n">
-        <v>7057109</v>
+        <v>7056939</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121144897</v>
+        <v>121145337</v>
       </c>
       <c r="B10" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,19 +1636,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592373</v>
+        <v>592484</v>
       </c>
       <c r="R10" t="n">
-        <v>7057122</v>
+        <v>7056961</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1679,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1689,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1704,22 +1710,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121145765</v>
+        <v>121145072</v>
       </c>
       <c r="B11" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,29 +1757,19 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592434</v>
+        <v>592412</v>
       </c>
       <c r="R11" t="n">
-        <v>7057127</v>
+        <v>7057010</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1805,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1815,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1830,22 +1826,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121145337</v>
+        <v>121144101</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>79682</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,47 +1850,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592484</v>
+        <v>592498</v>
       </c>
       <c r="R12" t="n">
-        <v>7056961</v>
+        <v>7057382</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1926,7 +1913,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1936,7 +1923,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,22 +1938,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121145481</v>
+        <v>121145668</v>
       </c>
       <c r="B13" t="n">
-        <v>57501</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,47 +1962,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592501</v>
+        <v>592435</v>
       </c>
       <c r="R13" t="n">
-        <v>7057009</v>
+        <v>7057094</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,7 +2029,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2057,7 +2039,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2084,10 +2066,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121145461</v>
+        <v>121145041</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2119,12 +2101,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2133,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592455</v>
+        <v>592409</v>
       </c>
       <c r="R14" t="n">
-        <v>7056968</v>
+        <v>7057036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2193,22 +2170,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121145366</v>
+        <v>121145461</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2240,7 +2217,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2254,10 +2231,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592468</v>
+        <v>592455</v>
       </c>
       <c r="R15" t="n">
-        <v>7056982</v>
+        <v>7056968</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2289,7 +2266,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2299,7 +2276,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2326,10 +2303,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121144953</v>
+        <v>121145444</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2361,7 +2338,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2370,10 +2347,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592355</v>
+        <v>592480</v>
       </c>
       <c r="R16" t="n">
-        <v>7057066</v>
+        <v>7057011</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121145874</v>
+        <v>121144873</v>
       </c>
       <c r="B17" t="n">
-        <v>91963</v>
+        <v>98081</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,38 +2431,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592503</v>
+        <v>592361</v>
       </c>
       <c r="R17" t="n">
-        <v>7057245</v>
+        <v>7057138</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,7 +2503,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,7 +2513,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2542,22 +2528,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121145691</v>
+        <v>121145765</v>
       </c>
       <c r="B18" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,7 +2575,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2597,16 +2583,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592431</v>
+        <v>592434</v>
       </c>
       <c r="R18" t="n">
-        <v>7057118</v>
+        <v>7057127</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2638,7 +2629,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2648,7 +2639,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2675,10 +2666,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121145281</v>
+        <v>121144921</v>
       </c>
       <c r="B19" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2710,19 +2701,19 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592450</v>
+        <v>592376</v>
       </c>
       <c r="R19" t="n">
-        <v>7056929</v>
+        <v>7057109</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2754,7 +2745,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2764,7 +2755,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2791,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121145312</v>
+        <v>121145691</v>
       </c>
       <c r="B20" t="n">
-        <v>78334</v>
+        <v>98081</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,38 +2794,47 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592474</v>
+        <v>592431</v>
       </c>
       <c r="R20" t="n">
-        <v>7056939</v>
+        <v>7057118</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,12 +2891,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121145281</v>
+        <v>121144798</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592450</v>
+        <v>592367</v>
       </c>
       <c r="R2" t="n">
-        <v>7056929</v>
+        <v>7057196</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121144953</v>
+        <v>121145281</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -835,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592355</v>
+        <v>592450</v>
       </c>
       <c r="R3" t="n">
-        <v>7057066</v>
+        <v>7056929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121144798</v>
+        <v>121144953</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,38 +915,42 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592367</v>
+        <v>592355</v>
       </c>
       <c r="R4" t="n">
-        <v>7057196</v>
+        <v>7057066</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121144798</v>
+        <v>121145281</v>
       </c>
       <c r="B2" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592367</v>
+        <v>592450</v>
       </c>
       <c r="R2" t="n">
-        <v>7057196</v>
+        <v>7056929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121145281</v>
+        <v>121144953</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -831,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592450</v>
+        <v>592355</v>
       </c>
       <c r="R3" t="n">
-        <v>7056929</v>
+        <v>7057066</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +870,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,7 +880,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121144953</v>
+        <v>121144798</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +919,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592355</v>
+        <v>592367</v>
       </c>
       <c r="R4" t="n">
-        <v>7057066</v>
+        <v>7057196</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121145281</v>
+        <v>121144897</v>
       </c>
       <c r="B2" t="n">
         <v>98081</v>
@@ -710,19 +710,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592450</v>
+        <v>592373</v>
       </c>
       <c r="R2" t="n">
-        <v>7056929</v>
+        <v>7057122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,7 +791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121144953</v>
+        <v>121144873</v>
       </c>
       <c r="B3" t="n">
         <v>98081</v>
@@ -826,19 +826,24 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592355</v>
+        <v>592361</v>
       </c>
       <c r="R3" t="n">
-        <v>7057066</v>
+        <v>7057138</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -880,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,22 +900,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121144798</v>
+        <v>121145691</v>
       </c>
       <c r="B4" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,38 +924,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592367</v>
+        <v>592431</v>
       </c>
       <c r="R4" t="n">
-        <v>7057196</v>
+        <v>7057118</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -992,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,19 +1021,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121144897</v>
+        <v>121145281</v>
       </c>
       <c r="B5" t="n">
         <v>98081</v>
@@ -1054,19 +1068,19 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592373</v>
+        <v>592450</v>
       </c>
       <c r="R5" t="n">
-        <v>7057122</v>
+        <v>7056929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1368,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121145481</v>
+        <v>121145765</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>98081</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1380,47 +1394,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592501</v>
+        <v>592434</v>
       </c>
       <c r="R8" t="n">
-        <v>7057009</v>
+        <v>7057127</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1452,7 +1471,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1462,7 +1481,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,22 +1496,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121145312</v>
+        <v>121144921</v>
       </c>
       <c r="B9" t="n">
-        <v>78337</v>
+        <v>98081</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1501,38 +1520,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592474</v>
+        <v>592376</v>
       </c>
       <c r="R9" t="n">
-        <v>7056939</v>
+        <v>7057109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1601,7 +1624,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121145337</v>
+        <v>121144953</v>
       </c>
       <c r="B10" t="n">
         <v>98081</v>
@@ -1636,12 +1659,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1650,10 +1668,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592484</v>
+        <v>592355</v>
       </c>
       <c r="R10" t="n">
-        <v>7056961</v>
+        <v>7057066</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1713,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,19 +1728,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121145072</v>
+        <v>121145444</v>
       </c>
       <c r="B11" t="n">
         <v>98081</v>
@@ -1757,7 +1775,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1766,10 +1784,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592412</v>
+        <v>592480</v>
       </c>
       <c r="R11" t="n">
-        <v>7057010</v>
+        <v>7057011</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1801,7 +1819,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1811,7 +1829,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1838,10 +1856,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121144101</v>
+        <v>121145481</v>
       </c>
       <c r="B12" t="n">
-        <v>79682</v>
+        <v>57504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,34 +1872,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592498</v>
+        <v>592501</v>
       </c>
       <c r="R12" t="n">
-        <v>7057382</v>
+        <v>7057009</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1913,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1923,7 +1950,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2066,7 +2093,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121145041</v>
+        <v>121145337</v>
       </c>
       <c r="B14" t="n">
         <v>98081</v>
@@ -2101,7 +2128,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2110,10 +2142,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592409</v>
+        <v>592484</v>
       </c>
       <c r="R14" t="n">
-        <v>7057036</v>
+        <v>7056961</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2145,7 +2177,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2155,7 +2187,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,19 +2202,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121145461</v>
+        <v>121145072</v>
       </c>
       <c r="B15" t="n">
         <v>98081</v>
@@ -2217,12 +2249,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2231,10 +2258,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592455</v>
+        <v>592412</v>
       </c>
       <c r="R15" t="n">
-        <v>7056968</v>
+        <v>7057010</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2266,7 +2293,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2276,7 +2303,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,22 +2318,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121145444</v>
+        <v>121144101</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2315,42 +2342,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592480</v>
+        <v>592498</v>
       </c>
       <c r="R16" t="n">
-        <v>7057011</v>
+        <v>7057382</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2382,7 +2405,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2415,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,10 +2442,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121144873</v>
+        <v>121145312</v>
       </c>
       <c r="B17" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,47 +2454,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592361</v>
+        <v>592474</v>
       </c>
       <c r="R17" t="n">
-        <v>7057138</v>
+        <v>7056939</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2503,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,7 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2528,22 +2542,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121145765</v>
+        <v>121144798</v>
       </c>
       <c r="B18" t="n">
-        <v>98081</v>
+        <v>78337</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2552,52 +2566,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592434</v>
+        <v>592367</v>
       </c>
       <c r="R18" t="n">
-        <v>7057127</v>
+        <v>7057196</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2639,7 +2639,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,19 +2654,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121144921</v>
+        <v>121145461</v>
       </c>
       <c r="B19" t="n">
         <v>98081</v>
@@ -2701,19 +2701,24 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592376</v>
+        <v>592455</v>
       </c>
       <c r="R19" t="n">
-        <v>7057109</v>
+        <v>7056968</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,7 +2750,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,7 +2760,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,19 +2775,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121145691</v>
+        <v>121145041</v>
       </c>
       <c r="B20" t="n">
         <v>98081</v>
@@ -2817,24 +2822,19 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592431</v>
+        <v>592409</v>
       </c>
       <c r="R20" t="n">
-        <v>7057118</v>
+        <v>7057036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,12 +2891,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121144897</v>
+        <v>121145461</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,19 +710,24 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592373</v>
+        <v>592455</v>
       </c>
       <c r="R2" t="n">
-        <v>7057122</v>
+        <v>7056968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,22 +784,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121144873</v>
+        <v>121145337</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -836,14 +841,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592361</v>
+        <v>592484</v>
       </c>
       <c r="R3" t="n">
-        <v>7057138</v>
+        <v>7056961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,10 +917,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121145691</v>
+        <v>121145281</v>
       </c>
       <c r="B4" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,24 +952,19 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592431</v>
+        <v>592450</v>
       </c>
       <c r="R4" t="n">
-        <v>7057118</v>
+        <v>7056929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,22 +1021,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121145281</v>
+        <v>121144798</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>78340</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,42 +1045,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592450</v>
+        <v>592367</v>
       </c>
       <c r="R5" t="n">
-        <v>7056929</v>
+        <v>7057196</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121145874</v>
+        <v>121145072</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1157,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592503</v>
+        <v>592412</v>
       </c>
       <c r="R6" t="n">
-        <v>7057245</v>
+        <v>7057010</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1261,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121145366</v>
+        <v>121144873</v>
       </c>
       <c r="B7" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592468</v>
+        <v>592361</v>
       </c>
       <c r="R7" t="n">
-        <v>7056982</v>
+        <v>7057138</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,10 +1382,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121145765</v>
+        <v>121145874</v>
       </c>
       <c r="B8" t="n">
-        <v>98081</v>
+        <v>91985</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,52 +1394,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592434</v>
+        <v>592503</v>
       </c>
       <c r="R8" t="n">
-        <v>7057127</v>
+        <v>7057245</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1457,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1481,7 +1467,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,22 +1482,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121144921</v>
+        <v>121145668</v>
       </c>
       <c r="B9" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,7 +1529,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1552,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592376</v>
+        <v>592435</v>
       </c>
       <c r="R9" t="n">
-        <v>7057109</v>
+        <v>7057094</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121144953</v>
+        <v>121145041</v>
       </c>
       <c r="B10" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1659,7 +1645,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1668,10 +1654,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592355</v>
+        <v>592409</v>
       </c>
       <c r="R10" t="n">
-        <v>7057066</v>
+        <v>7057036</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,7 +1689,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,7 +1699,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,10 +1726,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121145444</v>
+        <v>121145765</v>
       </c>
       <c r="B11" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1775,19 +1761,29 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592480</v>
+        <v>592434</v>
       </c>
       <c r="R11" t="n">
-        <v>7057011</v>
+        <v>7057127</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1819,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,22 +1840,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121145481</v>
+        <v>121145312</v>
       </c>
       <c r="B12" t="n">
-        <v>57504</v>
+        <v>78340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,43 +1868,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592501</v>
+        <v>592474</v>
       </c>
       <c r="R12" t="n">
-        <v>7057009</v>
+        <v>7056939</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1977,10 +1964,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121145668</v>
+        <v>121144921</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,7 +1999,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2021,10 +2008,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592435</v>
+        <v>592376</v>
       </c>
       <c r="R13" t="n">
-        <v>7057094</v>
+        <v>7057109</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2056,7 +2043,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2066,7 +2053,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2093,10 +2080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121145337</v>
+        <v>121145444</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2128,12 +2115,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2142,10 +2124,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592484</v>
+        <v>592480</v>
       </c>
       <c r="R14" t="n">
-        <v>7056961</v>
+        <v>7057011</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2177,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2187,7 +2169,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,22 +2184,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121145072</v>
+        <v>121145691</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2249,19 +2231,24 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592412</v>
+        <v>592431</v>
       </c>
       <c r="R15" t="n">
-        <v>7057010</v>
+        <v>7057118</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2293,7 +2280,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2303,7 +2290,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2318,22 +2305,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121144101</v>
+        <v>121145366</v>
       </c>
       <c r="B16" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2342,38 +2329,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592498</v>
+        <v>592468</v>
       </c>
       <c r="R16" t="n">
-        <v>7057382</v>
+        <v>7056982</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2405,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2415,7 +2411,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,22 +2426,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121145312</v>
+        <v>121144897</v>
       </c>
       <c r="B17" t="n">
-        <v>78337</v>
+        <v>98094</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2454,38 +2450,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592474</v>
+        <v>592373</v>
       </c>
       <c r="R17" t="n">
-        <v>7056939</v>
+        <v>7057122</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2554,10 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121144798</v>
+        <v>121144953</v>
       </c>
       <c r="B18" t="n">
-        <v>78337</v>
+        <v>98094</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2566,38 +2566,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592367</v>
+        <v>592355</v>
       </c>
       <c r="R18" t="n">
-        <v>7057196</v>
+        <v>7057066</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2666,10 +2670,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121145461</v>
+        <v>121145481</v>
       </c>
       <c r="B19" t="n">
-        <v>98081</v>
+        <v>57504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2678,35 +2682,35 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2715,10 +2719,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592455</v>
+        <v>592501</v>
       </c>
       <c r="R19" t="n">
-        <v>7056968</v>
+        <v>7057009</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2750,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2760,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2775,22 +2779,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121145041</v>
+        <v>121144101</v>
       </c>
       <c r="B20" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2799,42 +2803,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592409</v>
+        <v>592498</v>
       </c>
       <c r="R20" t="n">
-        <v>7057036</v>
+        <v>7057382</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121145461</v>
+        <v>121145366</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592455</v>
+        <v>592468</v>
       </c>
       <c r="R2" t="n">
-        <v>7056968</v>
+        <v>7056982</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121145337</v>
+        <v>121145444</v>
       </c>
       <c r="B3" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,12 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -845,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592484</v>
+        <v>592480</v>
       </c>
       <c r="R3" t="n">
-        <v>7056961</v>
+        <v>7057011</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,22 +900,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121145281</v>
+        <v>121145765</v>
       </c>
       <c r="B4" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,19 +947,29 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592450</v>
+        <v>592434</v>
       </c>
       <c r="R4" t="n">
-        <v>7056929</v>
+        <v>7057127</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,19 +1026,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121144798</v>
+        <v>121145312</v>
       </c>
       <c r="B5" t="n">
         <v>78340</v>
@@ -1069,14 +1074,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592367</v>
+        <v>592474</v>
       </c>
       <c r="R5" t="n">
-        <v>7057196</v>
+        <v>7056939</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1113,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1123,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121145072</v>
+        <v>121145337</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,7 +1185,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1199,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592412</v>
+        <v>592484</v>
       </c>
       <c r="R6" t="n">
-        <v>7057010</v>
+        <v>7056961</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1234,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1244,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,22 +1259,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121144873</v>
+        <v>121144921</v>
       </c>
       <c r="B7" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,12 +1306,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1310,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592361</v>
+        <v>592376</v>
       </c>
       <c r="R7" t="n">
-        <v>7057138</v>
+        <v>7057109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1350,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1360,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,22 +1375,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121145874</v>
+        <v>121145668</v>
       </c>
       <c r="B8" t="n">
-        <v>91985</v>
+        <v>98095</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,38 +1399,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592503</v>
+        <v>592435</v>
       </c>
       <c r="R8" t="n">
-        <v>7057245</v>
+        <v>7057094</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1457,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1467,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1494,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121145668</v>
+        <v>121145691</v>
       </c>
       <c r="B9" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,7 +1538,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1538,10 +1552,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592435</v>
+        <v>592431</v>
       </c>
       <c r="R9" t="n">
-        <v>7057094</v>
+        <v>7057118</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,22 +1612,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121145041</v>
+        <v>121144873</v>
       </c>
       <c r="B10" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,19 +1659,24 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592409</v>
+        <v>592361</v>
       </c>
       <c r="R10" t="n">
-        <v>7057036</v>
+        <v>7057138</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1689,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1699,7 +1718,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1714,22 +1733,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121145765</v>
+        <v>121145874</v>
       </c>
       <c r="B11" t="n">
-        <v>98094</v>
+        <v>91986</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,52 +1757,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592434</v>
+        <v>592503</v>
       </c>
       <c r="R11" t="n">
-        <v>7057127</v>
+        <v>7057245</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1820,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1830,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,22 +1845,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121145312</v>
+        <v>121144101</v>
       </c>
       <c r="B12" t="n">
-        <v>78340</v>
+        <v>79685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1868,34 +1873,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592474</v>
+        <v>592498</v>
       </c>
       <c r="R12" t="n">
-        <v>7056939</v>
+        <v>7057382</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1927,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,7 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121144921</v>
+        <v>121145281</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,19 +2004,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592376</v>
+        <v>592450</v>
       </c>
       <c r="R13" t="n">
-        <v>7057109</v>
+        <v>7056929</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2043,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2053,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2080,10 +2085,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121145444</v>
+        <v>121144953</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2115,7 +2120,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2124,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592480</v>
+        <v>592355</v>
       </c>
       <c r="R14" t="n">
-        <v>7057011</v>
+        <v>7057066</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2159,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2196,10 +2201,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121145691</v>
+        <v>121144798</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>78340</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2208,47 +2213,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592431</v>
+        <v>592367</v>
       </c>
       <c r="R15" t="n">
-        <v>7057118</v>
+        <v>7057196</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2276,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2290,7 +2286,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,22 +2301,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121145366</v>
+        <v>121145072</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,12 +2348,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2366,10 +2357,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592468</v>
+        <v>592412</v>
       </c>
       <c r="R16" t="n">
-        <v>7056982</v>
+        <v>7057010</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,7 +2392,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2411,7 +2402,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,12 +2417,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2441,7 +2432,7 @@
         <v>121144897</v>
       </c>
       <c r="B17" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2554,10 +2545,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121144953</v>
+        <v>121145461</v>
       </c>
       <c r="B18" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2589,7 +2580,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2598,10 +2594,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592355</v>
+        <v>592455</v>
       </c>
       <c r="R18" t="n">
-        <v>7057066</v>
+        <v>7056968</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,7 +2629,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2639,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,12 +2654,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2791,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121144101</v>
+        <v>121145041</v>
       </c>
       <c r="B20" t="n">
-        <v>79685</v>
+        <v>98095</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2803,38 +2799,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592498</v>
+        <v>592409</v>
       </c>
       <c r="R20" t="n">
-        <v>7057382</v>
+        <v>7057036</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121145366</v>
+        <v>121145461</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592468</v>
+        <v>592455</v>
       </c>
       <c r="R2" t="n">
-        <v>7056982</v>
+        <v>7056968</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121145444</v>
+        <v>121145366</v>
       </c>
       <c r="B3" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -831,7 +831,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -840,10 +845,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592480</v>
+        <v>592468</v>
       </c>
       <c r="R3" t="n">
-        <v>7057011</v>
+        <v>7056982</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +890,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,22 +905,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121145765</v>
+        <v>121145668</v>
       </c>
       <c r="B4" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,17 +952,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -966,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592434</v>
+        <v>592435</v>
       </c>
       <c r="R4" t="n">
-        <v>7057127</v>
+        <v>7057094</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,7 +996,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +1006,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,22 +1021,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121145312</v>
+        <v>121144101</v>
       </c>
       <c r="B5" t="n">
-        <v>78340</v>
+        <v>79688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,34 +1049,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592474</v>
+        <v>592498</v>
       </c>
       <c r="R5" t="n">
-        <v>7056939</v>
+        <v>7057382</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1113,7 +1108,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1123,7 +1118,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1150,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121145337</v>
+        <v>121145444</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1185,12 +1180,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1199,10 +1189,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592484</v>
+        <v>592480</v>
       </c>
       <c r="R6" t="n">
-        <v>7056961</v>
+        <v>7057011</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,7 +1224,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1244,7 +1234,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1259,22 +1249,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121144921</v>
+        <v>121145691</v>
       </c>
       <c r="B7" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1306,7 +1296,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1315,10 +1310,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592376</v>
+        <v>592431</v>
       </c>
       <c r="R7" t="n">
-        <v>7057109</v>
+        <v>7057118</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1350,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1360,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1375,22 +1370,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121145668</v>
+        <v>121144953</v>
       </c>
       <c r="B8" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,19 +1417,19 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592435</v>
+        <v>592355</v>
       </c>
       <c r="R8" t="n">
-        <v>7057094</v>
+        <v>7057066</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121145691</v>
+        <v>121145765</v>
       </c>
       <c r="B9" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,7 +1533,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1546,16 +1541,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592431</v>
+        <v>592434</v>
       </c>
       <c r="R9" t="n">
-        <v>7057118</v>
+        <v>7057127</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121144873</v>
+        <v>121145312</v>
       </c>
       <c r="B10" t="n">
-        <v>98095</v>
+        <v>78343</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,47 +1636,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592361</v>
+        <v>592474</v>
       </c>
       <c r="R10" t="n">
-        <v>7057138</v>
+        <v>7056939</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1708,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1733,22 +1724,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121145874</v>
+        <v>121145072</v>
       </c>
       <c r="B11" t="n">
-        <v>91986</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,38 +1748,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592503</v>
+        <v>592412</v>
       </c>
       <c r="R11" t="n">
-        <v>7057245</v>
+        <v>7057010</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1820,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1830,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1852,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121144101</v>
+        <v>121145337</v>
       </c>
       <c r="B12" t="n">
-        <v>79685</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,38 +1864,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592498</v>
+        <v>592484</v>
       </c>
       <c r="R12" t="n">
-        <v>7057382</v>
+        <v>7056961</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1932,7 +1936,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1942,7 +1946,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1957,22 +1961,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121145281</v>
+        <v>121144897</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2004,19 +2008,19 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592450</v>
+        <v>592373</v>
       </c>
       <c r="R13" t="n">
-        <v>7056929</v>
+        <v>7057122</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,7 +2062,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2085,10 +2089,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121144953</v>
+        <v>121145041</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,7 +2124,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2129,10 +2133,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592355</v>
+        <v>592409</v>
       </c>
       <c r="R14" t="n">
-        <v>7057066</v>
+        <v>7057036</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2164,7 +2168,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2174,7 +2178,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2201,10 +2205,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121144798</v>
+        <v>121145481</v>
       </c>
       <c r="B15" t="n">
-        <v>78340</v>
+        <v>57507</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2217,34 +2221,43 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592367</v>
+        <v>592501</v>
       </c>
       <c r="R15" t="n">
-        <v>7057196</v>
+        <v>7057009</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2276,7 +2289,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2286,7 +2299,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:39</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2313,10 +2326,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121145072</v>
+        <v>121145874</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>91989</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2325,42 +2338,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592412</v>
+        <v>592503</v>
       </c>
       <c r="R16" t="n">
-        <v>7057010</v>
+        <v>7057245</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2392,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2402,7 +2411,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2429,10 +2438,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121144897</v>
+        <v>121144921</v>
       </c>
       <c r="B17" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2464,7 +2473,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2473,10 +2482,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592373</v>
+        <v>592376</v>
       </c>
       <c r="R17" t="n">
-        <v>7057122</v>
+        <v>7057109</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2508,7 +2517,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2518,7 +2527,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2545,10 +2554,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121145461</v>
+        <v>121145281</v>
       </c>
       <c r="B18" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2580,12 +2589,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2594,10 +2598,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592455</v>
+        <v>592450</v>
       </c>
       <c r="R18" t="n">
-        <v>7056968</v>
+        <v>7056929</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2629,7 +2633,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2639,7 +2643,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2654,22 +2658,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121145481</v>
+        <v>121144798</v>
       </c>
       <c r="B19" t="n">
-        <v>57504</v>
+        <v>78343</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,43 +2686,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592501</v>
+        <v>592367</v>
       </c>
       <c r="R19" t="n">
-        <v>7057009</v>
+        <v>7057196</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2750,7 +2745,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2760,7 +2755,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:39</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2787,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121145041</v>
+        <v>121144873</v>
       </c>
       <c r="B20" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2822,19 +2817,24 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592409</v>
+        <v>592361</v>
       </c>
       <c r="R20" t="n">
-        <v>7057036</v>
+        <v>7057138</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,12 +2891,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>

--- a/artfynd/A 51340-2024 artfynd.xlsx
+++ b/artfynd/A 51340-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121145461</v>
+        <v>121144897</v>
       </c>
       <c r="B2" t="n">
         <v>98098</v>
@@ -710,24 +710,19 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592455</v>
+        <v>592373</v>
       </c>
       <c r="R2" t="n">
-        <v>7056968</v>
+        <v>7057122</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +754,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +764,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -784,22 +779,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121145366</v>
+        <v>121144101</v>
       </c>
       <c r="B3" t="n">
-        <v>98098</v>
+        <v>79688</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,47 +803,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592468</v>
+        <v>592498</v>
       </c>
       <c r="R3" t="n">
-        <v>7056982</v>
+        <v>7057382</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -880,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +876,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,19 +891,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121145668</v>
+        <v>121145461</v>
       </c>
       <c r="B4" t="n">
         <v>98098</v>
@@ -952,19 +938,24 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592435</v>
+        <v>592455</v>
       </c>
       <c r="R4" t="n">
-        <v>7057094</v>
+        <v>7056968</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1006,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,22 +1012,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121144101</v>
+        <v>121145072</v>
       </c>
       <c r="B5" t="n">
-        <v>79688</v>
+        <v>98098</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1045,38 +1036,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592498</v>
+        <v>592412</v>
       </c>
       <c r="R5" t="n">
-        <v>7057382</v>
+        <v>7057010</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,7 +1103,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1118,7 +1113,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,7 +1140,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121145444</v>
+        <v>121144953</v>
       </c>
       <c r="B6" t="n">
         <v>98098</v>
@@ -1180,7 +1175,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1189,10 +1184,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592480</v>
+        <v>592355</v>
       </c>
       <c r="R6" t="n">
-        <v>7057011</v>
+        <v>7057066</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1219,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1229,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,10 +1256,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121145691</v>
+        <v>121145312</v>
       </c>
       <c r="B7" t="n">
-        <v>98098</v>
+        <v>78343</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1273,47 +1268,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592431</v>
+        <v>592474</v>
       </c>
       <c r="R7" t="n">
-        <v>7057118</v>
+        <v>7056939</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1331,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1341,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,22 +1356,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121144953</v>
+        <v>121144798</v>
       </c>
       <c r="B8" t="n">
-        <v>98098</v>
+        <v>78343</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,42 +1380,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592355</v>
+        <v>592367</v>
       </c>
       <c r="R8" t="n">
-        <v>7057066</v>
+        <v>7057196</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1443,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1453,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1498,7 +1480,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121145765</v>
+        <v>121145337</v>
       </c>
       <c r="B9" t="n">
         <v>98098</v>
@@ -1533,7 +1515,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1541,21 +1523,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592434</v>
+        <v>592484</v>
       </c>
       <c r="R9" t="n">
-        <v>7057127</v>
+        <v>7056961</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1564,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1574,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1624,10 +1601,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121145312</v>
+        <v>121145366</v>
       </c>
       <c r="B10" t="n">
-        <v>78343</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,38 +1613,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592474</v>
+        <v>592468</v>
       </c>
       <c r="R10" t="n">
-        <v>7056939</v>
+        <v>7056982</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1699,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,19 +1710,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121145072</v>
+        <v>121145041</v>
       </c>
       <c r="B11" t="n">
         <v>98098</v>
@@ -1771,7 +1757,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1780,10 +1766,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592412</v>
+        <v>592409</v>
       </c>
       <c r="R11" t="n">
-        <v>7057010</v>
+        <v>7057036</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1815,7 +1801,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1825,7 +1811,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1852,7 +1838,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121145337</v>
+        <v>121145765</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1887,7 +1873,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>70</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1895,16 +1881,21 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592484</v>
+        <v>592434</v>
       </c>
       <c r="R12" t="n">
-        <v>7056961</v>
+        <v>7057127</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1936,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,7 +1964,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121144897</v>
+        <v>121144873</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -2008,7 +1999,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2017,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592373</v>
+        <v>592361</v>
       </c>
       <c r="R13" t="n">
-        <v>7057122</v>
+        <v>7057138</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2052,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2062,7 +2058,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,19 +2073,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121145041</v>
+        <v>121145281</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -2124,7 +2120,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2133,10 +2129,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592409</v>
+        <v>592450</v>
       </c>
       <c r="R14" t="n">
-        <v>7057036</v>
+        <v>7056929</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2168,7 +2164,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2178,7 +2174,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2326,10 +2322,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121145874</v>
+        <v>121145668</v>
       </c>
       <c r="B16" t="n">
-        <v>91989</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2338,38 +2334,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592503</v>
+        <v>592435</v>
       </c>
       <c r="R16" t="n">
-        <v>7057245</v>
+        <v>7057094</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2401,7 +2401,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2554,7 +2554,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121145281</v>
+        <v>121145691</v>
       </c>
       <c r="B18" t="n">
         <v>98098</v>
@@ -2589,19 +2589,24 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Skutåsen, Skutåsen, Ång</t>
+          <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592450</v>
+        <v>592431</v>
       </c>
       <c r="R18" t="n">
-        <v>7056929</v>
+        <v>7057118</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2633,7 +2638,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2643,7 +2648,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,22 +2663,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121144798</v>
+        <v>121145444</v>
       </c>
       <c r="B19" t="n">
-        <v>78343</v>
+        <v>98098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2682,38 +2687,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Rörviken, Rörviken, Ång</t>
+          <t>Skutåsen, Skutåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592367</v>
+        <v>592480</v>
       </c>
       <c r="R19" t="n">
-        <v>7057196</v>
+        <v>7057011</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2745,7 +2754,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2755,7 +2764,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,10 +2791,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121144873</v>
+        <v>121145874</v>
       </c>
       <c r="B20" t="n">
-        <v>98098</v>
+        <v>91989</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,47 +2803,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Rörviken, Rörviken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592361</v>
+        <v>592503</v>
       </c>
       <c r="R20" t="n">
-        <v>7057138</v>
+        <v>7057245</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,12 +2891,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
